--- a/stories/arbres/ATOM-DIF.BES.002-02.xlsx
+++ b/stories/arbres/ATOM-DIF.BES.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV7"/>
+  <dimension ref="A1:AW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1285,6 +1301,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le sable est chaud. Un oiseau chante. Lila a envie de jouer.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1309,7 +1330,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Lila est au parc avec maman. Kenzo est près du bac. Lila va proposer le seau. Elle dit : tu viens ? Kenzo dit : je regarde. Lila accepte. Maman dit : on peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard. Lila creuse. Kenzo reste au bord. Lila propose encore, tout doux : plus tard ? Kenzo dit : plus tard. Lila dit : d'accord. Elle accepte plusieurs réponses.</t>
+          <t>Lila est au parc avec maman. Kenzo est près du bac. Lila va proposer le seau. Tu viens ? Je regarde. Lila accepte. On peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard. Lila creuse. Kenzo reste au bord. Lila propose encore, tout doux : plus tard ? Plus tard. D'accord. Elle accepte plusieurs réponses.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1447,6 +1468,18 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Lila est au parc avec maman. Kenzo est près du bac. Lila va proposer le seau.
+narrateur|Tu viens ?
+copain|Je regarde.
+narrateur|Lila accepte.
+maman|On peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard.
+narrateur|Lila creuse. Kenzo reste au bord. Lila propose encore, tout doux : plus tard ?
+copain|Plus tard.
+enfant-f|D'accord. Elle accepte plusieurs réponses.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1623,6 +1656,11 @@
       <c r="AV4" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lila invite Kenzo. Que fait-elle si Kenzo dit non ?</t>
         </is>
       </c>
     </row>
@@ -1791,6 +1829,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a su proposer. Elle a su accepter plusieurs réponses.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range le seau. Lila donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2115,6 +2163,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV7"/>
@@ -2133,7 +2186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2150,6 +2203,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.BES.002-02.xlsx
+++ b/stories/arbres/ATOM-DIF.BES.002-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW7"/>
+  <dimension ref="A1:AX7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1306,6 +1311,7 @@
           <t>narrateur|Le sable est chaud. Un oiseau chante. Lila a envie de jouer.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1480,6 +1486,11 @@
 enfant-f|D'accord. Elle accepte plusieurs réponses.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1663,6 +1674,7 @@
           <t>narrateur|Lila invite Kenzo. Que fait-elle si Kenzo dit non ?</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1846,7 @@
           <t>narrateur|Lila a su proposer. Elle a su accepter plusieurs réponses.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2014,7 @@
           <t>narrateur|Maman range le seau. Lila donne la main.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2168,6 +2182,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV7"/>
@@ -2186,7 +2201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2210,6 +2225,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2411,6 +2440,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-DIF.BES.002-02.xlsx
+++ b/stories/arbres/ATOM-DIF.BES.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lila propose le bac à sable</t>
+          <t>Mila propose le bac à sable</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DIF.BES.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila creuse avec le seau jaune. Elle propose. Aniss regarde, puis dit plus tard. Mila accepte.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le sable est chaud. Un oiseau chante. Lila a envie de jouer.</t>
+          <t>Les tilleuls du parc font une ombre. L'ombre bouge un peu. Le sable est chaud sous les doigts. Un oiseau répète la même note. Une sonnette de vélo, tout loin. Le seau jaune dort près du râteau. Le râteau est vert. Je mets le tissu sur le banc. Je verse de l'eau dans la bouteille. Tu entends l'oiseau, Mila ? Oui, maman. Le sable est chaud, hein ? Oui, papa. Juste maintenant, Mila a les mains dans le sable. Le sable colle un peu. Elle a envie de jouer.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1308,10 +1325,29 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le sable est chaud. Un oiseau chante. Lila a envie de jouer.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Les tilleuls du parc font une ombre.
+narrateur|L'ombre bouge un peu.
+narrateur|Le sable est chaud sous les doigts.
+narrateur|Un oiseau répète la même note.
+narrateur|Une sonnette de vélo, tout loin.
+narrateur|Le seau jaune dort près du râteau.
+narrateur|Le râteau est vert.
+maman|Je mets le tissu sur le banc.
+papa|Je verse de l'eau dans la bouteille.
+maman|Tu entends l'oiseau, Mila ?
+enfant-f|Oui, maman.
+papa|Le sable est chaud, hein ?
+enfant-f|Oui, papa.
+narrateur|Juste maintenant, Mila a les mains dans le sable.
+narrateur|Le sable colle un peu.
+narrateur|Elle a envie de jouer.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1336,7 +1372,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Lila est au parc avec maman. Kenzo est près du bac. Lila va proposer le seau. Tu viens ? Je regarde. Lila accepte. On peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard. Lila creuse. Kenzo reste au bord. Lila propose encore, tout doux : plus tard ? Plus tard. D'accord. Elle accepte plusieurs réponses.</t>
+          <t>Aniss est près du bac. Ses chaussures sont sablées. Mila prend le seau jaune. Tu viens ? Je regarde. Mila accepte. On peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard. Mila creuse. Le sable fait un petit bruit. Aniss reste au bord. Il regarde le trou. Plus tard ? Plus tard. D'accord. Tu as accepté, Mila ? Oui, papa. Regarder, c'est une réponse. Mila verse le sable dans le seau. Le seau devient lourd. Aniss avance un pied. Puis il s'arrête. C'est bien. Tu veux le râteau ? Non. D'accord. Plusieurs réponses sont possibles. Bravo, Mila. Tu as su proposer. Tu as su accepter. C'est du bon travail. L'oiseau chante encore. La sonnette est plus loin. Mila continue son trou. Aniss regarde.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1476,14 +1512,45 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Lila est au parc avec maman. Kenzo est près du bac. Lila va proposer le seau.
-narrateur|Tu viens ?
+          <t>narrateur|Aniss est près du bac.
+narrateur|Ses chaussures sont sablées.
+narrateur|Mila prend le seau jaune.
+enfant-f|Tu viens ?
 copain|Je regarde.
-narrateur|Lila accepte.
-maman|On peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard.
-narrateur|Lila creuse. Kenzo reste au bord. Lila propose encore, tout doux : plus tard ?
+narrateur|Mila accepte.
+maman|On peut proposer.
+maman|On peut accepter plusieurs réponses.
+papa|Oui.
+papa|Non.
+papa|Regarder.
+papa|Plus tard.
+narrateur|Mila creuse.
+narrateur|Le sable fait un petit bruit.
+narrateur|Aniss reste au bord.
+narrateur|Il regarde le trou.
+enfant-f|Plus tard ?
 copain|Plus tard.
-enfant-f|D'accord. Elle accepte plusieurs réponses.</t>
+enfant-f|D'accord.
+papa|Tu as accepté, Mila ?
+enfant-f|Oui, papa.
+maman|Regarder, c'est une réponse.
+narrateur|Mila verse le sable dans le seau.
+narrateur|Le seau devient lourd.
+narrateur|Aniss avance un pied.
+narrateur|Puis il s'arrête.
+maman|C'est bien.
+enfant-f|Tu veux le râteau ?
+copain|Non.
+enfant-f|D'accord.
+papa|Plusieurs réponses sont possibles.
+papa|Bravo, Mila.
+maman|Tu as su proposer.
+maman|Tu as su accepter.
+maman|C'est du bon travail.
+narrateur|L'oiseau chante encore.
+narrateur|La sonnette est plus loin.
+narrateur|Mila continue son trou.
+narrateur|Aniss regarde.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1515,7 +1582,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lila invite Kenzo. Que fait-elle si Kenzo dit non ?</t>
+          <t>Mila invite Aniss. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1671,7 +1738,8 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Lila invite Kenzo. Que fait-elle si Kenzo dit non ?</t>
+          <t>narrateur|Mila invite Aniss.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1699,7 +1767,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Lila a su proposer. Elle a su accepter plusieurs réponses.</t>
+          <t>Mila a su proposer. Elle a su accepter plusieurs réponses. Aniss a dit regarder, puis plus tard. Oui. Tout ça va. J'ai dit d'accord. Bravo. Tu as fait du bon travail. Le seau jaune est plein. Le sable brille encore.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1843,7 +1911,16 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Lila a su proposer. Elle a su accepter plusieurs réponses.</t>
+          <t>narrateur|Mila a su proposer.
+narrateur|Elle a su accepter plusieurs réponses.
+papa|Aniss a dit regarder, puis plus tard.
+maman|Oui.
+maman|Tout ça va.
+enfant-f|J'ai dit d'accord.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le seau jaune est plein.
+narrateur|Le sable brille encore.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1871,7 +1948,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Maman range le seau. Lila donne la main.</t>
+          <t>On range le seau ? Maman tape un peu le seau. Le sable tombe. Tu as fini de jouer, Mila ? Oui, papa. Bravo. Mila donne la main. Aniss secoue ses chaussures. Merci, Aniss. Le banc reste à l'ombre. L'oiseau se tait un moment.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2011,7 +2088,17 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Maman range le seau. Lila donne la main.</t>
+          <t>maman|On range le seau ?
+narrateur|Maman tape un peu le seau.
+narrateur|Le sable tombe.
+papa|Tu as fini de jouer, Mila ?
+enfant-f|Oui, papa.
+papa|Bravo.
+narrateur|Mila donne la main.
+narrateur|Aniss secoue ses chaussures.
+maman|Merci, Aniss.
+narrateur|Le banc reste à l'ombre.
+narrateur|L'oiseau se tait un moment.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2039,7 +2126,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé. J'ai accepté. Bravo. Tu as fait du bon travail. Le seau jaune dort près du râteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2179,7 +2266,12 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai proposé.
+enfant-f|J'ai accepté.
+maman|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le seau jaune dort près du râteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2201,7 +2293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2331,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.BES.002-02.xlsx
+++ b/stories/arbres/ATOM-DIF.BES.002-02.xlsx
@@ -1372,7 +1372,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Aniss est près du bac. Ses chaussures sont sablées. Mila prend le seau jaune. Tu viens ? Je regarde. Mila accepte. On peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard. Mila creuse. Le sable fait un petit bruit. Aniss reste au bord. Il regarde le trou. Plus tard ? Plus tard. D'accord. Tu as accepté, Mila ? Oui, papa. Regarder, c'est une réponse. Mila verse le sable dans le seau. Le seau devient lourd. Aniss avance un pied. Puis il s'arrête. C'est bien. Tu veux le râteau ? Non. D'accord. Plusieurs réponses sont possibles. Bravo, Mila. Tu as su proposer. Tu as su accepter. C'est du bon travail. L'oiseau chante encore. La sonnette est plus loin. Mila continue son trou. Aniss regarde.</t>
+          <t>Aniss est près du bac. Ses chaussures sont sablées. Mila prend le seau jaune. Tu viens ? Je regarde. Mila accepte. On peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard. Mila creuse. Le sable fait un petit bruit. Aniss reste au bord. Il regarde le trou. Plus tard ? Plus tard. D'accord. Tu as accepté, Mila ? Oui, papa. Regarder, c'est une réponse. Mila verse le sable dans le seau. Le seau devient lourd. Aniss avance un pied. Puis il s'arrête. C'est bien. Tu veux le râteau ? Non. D'accord. Plusieurs réponses sont possibles. Bravo, Mila. Tu as su proposer. Tu as su accepter. C'est du bon travail. L'oiseau chante encore. La sonnette est plus loin. Mila continue son trou. Aniss regarde. Le sable chaud colle aux genoux. Une feuille de tilleul tombe dans le bac. Tu la vois, Mila ? Oui. Mila pose la feuille au bord. Aniss avance la main. Puis il la retire. Tu as accepté sa réponse ? Oui, papa. Bravo. Le seau jaune est lourd maintenant. Mila le bascule. Un château tout petit apparaît. C'est joli. Aniss a regardé. Regarder, c'est une réponse.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1550,7 +1550,23 @@
 narrateur|L'oiseau chante encore.
 narrateur|La sonnette est plus loin.
 narrateur|Mila continue son trou.
-narrateur|Aniss regarde.</t>
+narrateur|Aniss regarde.
+narrateur|Le sable chaud colle aux genoux.
+narrateur|Une feuille de tilleul tombe dans le bac.
+maman|Tu la vois, Mila ?
+enfant-f|Oui.
+narrateur|Mila pose la feuille au bord.
+narrateur|Aniss avance la main.
+narrateur|Puis il la retire.
+papa|Tu as accepté sa réponse ?
+enfant-f|Oui, papa.
+maman|Bravo.
+narrateur|Le seau jaune est lourd maintenant.
+narrateur|Mila le bascule.
+narrateur|Un château tout petit apparaît.
+papa|C'est joli.
+enfant-f|Aniss a regardé.
+maman|Regarder, c'est une réponse.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -2293,7 +2309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2336,6 +2352,27 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-DIF.BES.002-02.xlsx
+++ b/stories/arbres/ATOM-DIF.BES.002-02.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mila propose le bac à sable</t>
+          <t>Le cerf-volant de papier</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mila creuse avec le seau jaune. Elle propose. Aniss regarde, puis dit plus tard. Mila accepte.</t>
+          <t>Mila veut que son cerf-volant de papier se lève au-dessus de la lavande. Elle propose. Aniss dit je regarde, puis plus tard, puis non pour la ficelle. Mila accepte. Une abeille passe. L'ombre du cerf-volant glisse sur les fleurs.</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les tilleuls du parc font une ombre. L'ombre bouge un peu. Le sable est chaud sous les doigts. Un oiseau répète la même note. Une sonnette de vélo, tout loin. Le seau jaune dort près du râteau. Le râteau est vert. Je mets le tissu sur le banc. Je verse de l'eau dans la bouteille. Tu entends l'oiseau, Mila ? Oui, maman. Le sable est chaud, hein ? Oui, papa. Juste maintenant, Mila a les mains dans le sable. Le sable colle un peu. Elle a envie de jouer.</t>
+          <t>La pierre de la terrasse est encore chaude. La lavande sent fort, tout près. Des tiges violettes bougent un peu. Des cigales chantent dans l'olivier. Un cerf-volant de papier attend sur la chaise. Il est bleu, avec une queue blanche. La ficelle est enroulée, un peu rêche. Je pose le chapeau sur le banc. Je remplis le verre d'eau. Tu entends les cigales, Mila ? Oui, maman. La pierre est chaude, hein ? Oui, papa. Je veux qu'il se lève. Au-dessus de la lavande. Un tout petit vent suffit. En ce moment, Mila prend le papier. Il est léger et un peu froissé.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le sable est chaud. Un oiseau chante. Lila a envie de jouer.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La pierre de la terrasse est encore chaude. La lavande sent fort, tout près. Des tiges violettes bougent un peu. Des cigales chantent dans l'olivier. Un cerf-volant de papier attend sur la chaise. Il est bleu, avec une queue blanche. La ficelle est enroulée, un peu rêche. Je pose le chapeau sur le banc. Je remplis le verre d'eau. Tu entends les cigales, Mila ? Oui, maman. La pierre est chaude, hein ? Oui, papa. Je veux qu'il se lève. Au-dessus de la lavande. Un tout petit vent suffit. En ce moment, Mila prend le papier. Il est léger et un peu froissé.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1325,27 +1325,29 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Les tilleuls du parc font une ombre.
-narrateur|L'ombre bouge un peu.
-narrateur|Le sable est chaud sous les doigts.
-narrateur|Un oiseau répète la même note.
-narrateur|Une sonnette de vélo, tout loin.
-narrateur|Le seau jaune dort près du râteau.
-narrateur|Le râteau est vert.
-maman|Je mets le tissu sur le banc.
-papa|Je verse de l'eau dans la bouteille.
-maman|Tu entends l'oiseau, Mila ?
+          <t>narrateur|La pierre de la terrasse est encore chaude.
+narrateur|La lavande sent fort, tout près.
+narrateur|Des tiges violettes bougent un peu.
+narrateur|Des cigales chantent dans l'olivier.
+narrateur|Un cerf-volant de papier attend sur la chaise.
+narrateur|Il est bleu, avec une queue blanche.
+narrateur|La ficelle est enroulée, un peu rêche.
+maman|Je pose le chapeau sur le banc.
+papa|Je remplis le verre d'eau.
+maman|Tu entends les cigales, Mila ?
 enfant-f|Oui, maman.
-papa|Le sable est chaud, hein ?
+papa|La pierre est chaude, hein ?
 enfant-f|Oui, papa.
-narrateur|Juste maintenant, Mila a les mains dans le sable.
-narrateur|Le sable colle un peu.
-narrateur|Elle a envie de jouer.</t>
+enfant-f|Je veux qu'il se lève.
+enfant-f|Au-dessus de la lavande.
+maman|Un tout petit vent suffit.
+narrateur|En ce moment, Mila prend le papier.
+narrateur|Il est léger et un peu froissé.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>terrasse,cigales</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1374,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Aniss est près du bac. Ses chaussures sont sablées. Mila prend le seau jaune. Tu viens ? Je regarde. Mila accepte. On peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard. Mila creuse. Le sable fait un petit bruit. Aniss reste au bord. Il regarde le trou. Plus tard ? Plus tard. D'accord. Tu as accepté, Mila ? Oui, papa. Regarder, c'est une réponse. Mila verse le sable dans le seau. Le seau devient lourd. Aniss avance un pied. Puis il s'arrête. C'est bien. Tu veux le râteau ? Non. D'accord. Plusieurs réponses sont possibles. Bravo, Mila. Tu as su proposer. Tu as su accepter. C'est du bon travail. L'oiseau chante encore. La sonnette est plus loin. Mila continue son trou. Aniss regarde. Le sable chaud colle aux genoux. Une feuille de tilleul tombe dans le bac. Tu la vois, Mila ? Oui. Mila pose la feuille au bord. Aniss avance la main. Puis il la retire. Tu as accepté sa réponse ? Oui, papa. Bravo. Le seau jaune est lourd maintenant. Mila le bascule. Un château tout petit apparaît. C'est joli. Aniss a regardé. Regarder, c'est une réponse.</t>
+          <t>Aniss est sur la marche. Ses pieds restent à l'ombre. Mila tient la ficelle. Tu viens ? Je regarde. Mila accepte. On peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard. D'accord. Mila lève le papier. Le vent le fait trembler. Aniss reste sur la marche. Il regarde la queue blanche. Plus tard ? Plus tard. D'accord. Tu as accepté, Mila ? Oui, papa. Regarder, c'est une réponse. Une abeille passe sur la lavande. Elle fait un petit bruit. Tu l'entends, Mila ? Oui. On attend qu'elle parte. Mila tient le papier bas. L'abeille s'en va. Tu veux la ficelle ? Non. D'accord. Plusieurs réponses sont possibles. Le cerf-volant tremble encore. Aniss avance un pied. Puis il le retire.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Lila est au parc avec maman. Kenzo est près du bac. Lila va &lt;emphasis level="moderate"&gt;proposer&lt;/emphasis&gt; le seau. Elle dit : tu viens ? Kenzo dit : je regarde. Lila accepte. Maman dit : on peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard. Lila creuse. Kenzo reste au bord. Lila propose encore, tout doux : plus tard ? Kenzo dit : plus tard. Lila dit : d'accord. Elle accepte plusieurs réponses.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss est sur la marche. Ses pieds restent à l'ombre. Mila tient la ficelle. Tu viens ? Je regarde. Mila accepte. On peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard. D'accord. Mila lève le papier. Le vent le fait trembler. Aniss reste sur la marche. Il regarde la queue blanche. Plus tard ? Plus tard. D'accord. Tu as accepté, Mila ? Oui, papa. Regarder, c'est une réponse. Une abeille passe sur la lavande. Elle fait un petit bruit. Tu l'entends, Mila ? Oui. On attend qu'elle parte. Mila tient le papier bas. L'abeille s'en va. Tu veux la ficelle ? Non. D'accord. Plusieurs réponses sont possibles. Le cerf-volant tremble encore. Aniss avance un pied. Puis il le retire.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1440,7 +1442,7 @@
         <v>0.92</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1512,9 +1514,9 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Aniss est près du bac.
-narrateur|Ses chaussures sont sablées.
-narrateur|Mila prend le seau jaune.
+          <t>narrateur|Aniss est sur la marche.
+narrateur|Ses pieds restent à l'ombre.
+narrateur|Mila tient la ficelle.
 enfant-f|Tu viens ?
 copain|Je regarde.
 narrateur|Mila accepte.
@@ -1524,54 +1526,36 @@
 papa|Non.
 papa|Regarder.
 papa|Plus tard.
-narrateur|Mila creuse.
-narrateur|Le sable fait un petit bruit.
-narrateur|Aniss reste au bord.
-narrateur|Il regarde le trou.
+enfant-f|D'accord.
+narrateur|Mila lève le papier.
+narrateur|Le vent le fait trembler.
+narrateur|Aniss reste sur la marche.
+narrateur|Il regarde la queue blanche.
 enfant-f|Plus tard ?
 copain|Plus tard.
 enfant-f|D'accord.
 papa|Tu as accepté, Mila ?
 enfant-f|Oui, papa.
 maman|Regarder, c'est une réponse.
-narrateur|Mila verse le sable dans le seau.
-narrateur|Le seau devient lourd.
-narrateur|Aniss avance un pied.
-narrateur|Puis il s'arrête.
-maman|C'est bien.
-enfant-f|Tu veux le râteau ?
+narrateur|Une abeille passe sur la lavande.
+narrateur|Elle fait un petit bruit.
+maman|Tu l'entends, Mila ?
+enfant-f|Oui.
+papa|On attend qu'elle parte.
+narrateur|Mila tient le papier bas.
+narrateur|L'abeille s'en va.
+enfant-f|Tu veux la ficelle ?
 copain|Non.
 enfant-f|D'accord.
 papa|Plusieurs réponses sont possibles.
-papa|Bravo, Mila.
-maman|Tu as su proposer.
-maman|Tu as su accepter.
-maman|C'est du bon travail.
-narrateur|L'oiseau chante encore.
-narrateur|La sonnette est plus loin.
-narrateur|Mila continue son trou.
-narrateur|Aniss regarde.
-narrateur|Le sable chaud colle aux genoux.
-narrateur|Une feuille de tilleul tombe dans le bac.
-maman|Tu la vois, Mila ?
-enfant-f|Oui.
-narrateur|Mila pose la feuille au bord.
-narrateur|Aniss avance la main.
-narrateur|Puis il la retire.
-papa|Tu as accepté sa réponse ?
-enfant-f|Oui, papa.
-maman|Bravo.
-narrateur|Le seau jaune est lourd maintenant.
-narrateur|Mila le bascule.
-narrateur|Un château tout petit apparaît.
-papa|C'est joli.
-enfant-f|Aniss a regardé.
-maman|Regarder, c'est une réponse.</t>
+narrateur|Le cerf-volant tremble encore.
+narrateur|Aniss avance un pied.
+narrateur|Puis il le retire.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>vent,papier</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1587,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Lila invite Kenzo. Que fait-elle si Kenzo dit non ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila invite Aniss. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1633,7 +1617,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Elle propose. Kenzo peut regarder. Que fait Lila ?</t>
+          <t>Elle propose. Aniss peut regarder. Que fait Mila ?</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
@@ -1682,7 +1666,7 @@
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1758,7 +1742,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1783,12 +1766,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Mila a su proposer. Elle a su accepter plusieurs réponses. Aniss a dit regarder, puis plus tard. Oui. Tout ça va. J'ai dit d'accord. Bravo. Tu as fait du bon travail. Le seau jaune est plein. Le sable brille encore.</t>
+          <t>Mila a su proposer. Elle a su accepter plusieurs réponses. Aniss a dit regarder, puis plus tard. Oui. Tout ça va. J'ai dit d'accord. Bravo. Tu as tenu la ficelle. Le papier se lève un peu. L'ombre passe sur la lavande. Tu vois l'ombre, Aniss ? Je regarde. C'est une réponse. Mila recule d'un pas. La queue blanche danse. Une tige de lavande se plie. Le vent est juste assez.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Lila a su &lt;emphasis level="moderate"&gt;proposer&lt;/emphasis&gt;. Elle a su accepter plusieurs réponses.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a su proposer. Elle a su accepter plusieurs réponses. Aniss a dit regarder, puis plus tard. Oui. Tout ça va. J'ai dit d'accord. Bravo. Tu as tenu la ficelle. Le papier se lève un peu. L'ombre passe sur la lavande. Tu vois l'ombre, Aniss ? Je regarde. C'est une réponse. Mila recule d'un pas. La queue blanche danse. Une tige de lavande se plie. Le vent est juste assez.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1851,7 +1834,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1934,12 +1917,23 @@
 maman|Tout ça va.
 enfant-f|J'ai dit d'accord.
 papa|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|Le seau jaune est plein.
-narrateur|Le sable brille encore.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+papa|Tu as tenu la ficelle.
+narrateur|Le papier se lève un peu.
+narrateur|L'ombre passe sur la lavande.
+enfant-f|Tu vois l'ombre, Aniss ?
+copain|Je regarde.
+maman|C'est une réponse.
+narrateur|Mila recule d'un pas.
+narrateur|La queue blanche danse.
+narrateur|Une tige de lavande se plie.
+papa|Le vent est juste assez.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>vent</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1964,12 +1958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On range le seau ? Maman tape un peu le seau. Le sable tombe. Tu as fini de jouer, Mila ? Oui, papa. Bravo. Mila donne la main. Aniss secoue ses chaussures. Merci, Aniss. Le banc reste à l'ombre. L'oiseau se tait un moment.</t>
+          <t>On repose le papier ? Encore un peu. L'ombre glisse sur deux tiges. Aniss suit des yeux. Tu as fini de jouer, Mila ? Oui, papa. Mila pose le cerf-volant. Il retrouve la chaise. Aniss secoue un pied. Un peu de poussière tombe. Merci, Aniss. Tu as regardé. La lavande sent encore. L'ombre était jolie. Oui.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman range le seau. Lila donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On repose le papier ? Encore un peu. L'ombre glisse sur deux tiges. Aniss suit des yeux. Tu as fini de jouer, Mila ? Oui, papa. Mila pose le cerf-volant. Il retrouve la chaise. Aniss secoue un pied. Un peu de poussière tombe. Merci, Aniss. Tu as regardé. La lavande sent encore. L'ombre était jolie. Oui.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2104,20 +2098,23 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>maman|On range le seau ?
-narrateur|Maman tape un peu le seau.
-narrateur|Le sable tombe.
+          <t>maman|On repose le papier ?
+enfant-f|Encore un peu.
+narrateur|L'ombre glisse sur deux tiges.
+narrateur|Aniss suit des yeux.
 papa|Tu as fini de jouer, Mila ?
 enfant-f|Oui, papa.
-papa|Bravo.
-narrateur|Mila donne la main.
-narrateur|Aniss secoue ses chaussures.
+narrateur|Mila pose le cerf-volant.
+narrateur|Il retrouve la chaise.
+narrateur|Aniss secoue un pied.
+narrateur|Un peu de poussière tombe.
 maman|Merci, Aniss.
-narrateur|Le banc reste à l'ombre.
-narrateur|L'oiseau se tait un moment.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Tu as regardé.
+papa|La lavande sent encore.
+enfant-f|L'ombre était jolie.
+papa|Oui.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2142,12 +2139,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>J'ai proposé. J'ai accepté. Bravo. Tu as fait du bon travail. Le seau jaune dort près du râteau. L'histoire est finie.</t>
+          <t>Le cerf-volant bleu dort sur la chaise. J'ai proposé. J'ai accepté. Plusieurs réponses sont possibles. Oui. Les cigales chantent encore. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le cerf-volant bleu dort sur la chaise. J'ai proposé. J'ai accepté. Plusieurs réponses sont possibles. Oui. Les cigales chantent encore. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2203,14 +2200,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA7" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
@@ -2282,15 +2279,15 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>enfant-f|J'ai proposé.
+          <t>narrateur|Le cerf-volant bleu dort sur la chaise.
+enfant-f|J'ai proposé.
 enfant-f|J'ai accepté.
-maman|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|Le seau jaune dort près du râteau.
+maman|Plusieurs réponses sont possibles.
+papa|Oui.
+narrateur|Les cigales chantent encore.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV7"/>
@@ -2309,7 +2306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2375,6 +2372,13 @@
       <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.BES.002-02.xlsx
+++ b/stories/arbres/ATOM-DIF.BES.002-02.xlsx
@@ -2139,12 +2139,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Le cerf-volant bleu dort sur la chaise. J'ai proposé. J'ai accepté. Plusieurs réponses sont possibles. Oui. Les cigales chantent encore. L'histoire est finie.</t>
+          <t>Le cerf-volant bleu dort sur la chaise. J'ai proposé. J'ai accepté. Plusieurs réponses sont possibles. Oui. Les cigales chantent encore.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Le cerf-volant bleu dort sur la chaise. J'ai proposé. J'ai accepté. Plusieurs réponses sont possibles. Oui. Les cigales chantent encore. L'histoire est finie.</t>
+          <t>Le cerf-volant bleu dort sur la chaise. J'ai proposé. J'ai accepté. Plusieurs réponses sont possibles. Oui. Les cigales chantent encore.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2284,8 +2284,7 @@
 enfant-f|J'ai accepté.
 maman|Plusieurs réponses sont possibles.
 papa|Oui.
-narrateur|Les cigales chantent encore.
-narrateur|L'histoire est finie.</t>
+narrateur|Les cigales chantent encore.</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2377,6 +2376,13 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-DIF.BES.002-02.xlsx
+++ b/stories/arbres/ATOM-DIF.BES.002-02.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parc</t>
+          <t>terrasse, lavande, après la sieste</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lila, Kenzo, maman</t>
+          <t>Mila, Aniss, papa, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.BES.002-02.xlsx
+++ b/stories/arbres/ATOM-DIF.BES.002-02.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>terrasse, lavande, après la sieste</t>
+          <t>terrasse, lavande, après la sieste, pierre chaude, tiges violettes</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mila veut que son cerf-volant de papier se lève au-dessus de la lavande. Elle propose. Aniss dit je regarde, puis plus tard, puis non pour la ficelle. Mila accepte. Une abeille passe. L'ombre du cerf-volant glisse sur les fleurs.</t>
+          <t>La pierre de la terrasse tient la chaleur. Sur la pierre, un éclat de pierre brille. Mila veut le cerf-volant au-dessus des tiges, maintenant. Elle lève trop vite : le papier tombe. Sourire parti. Elle tend la ficelle à Aniss : il retire les doigts, il regarde. Elle refuse de foncer, attend, dit d'accord. Merci vécu. Elle tire d'un coup : le papier plonge. Elle s'arrête, lit l'éclat, recule. Un éclat de pierre reste pâle.</t>
         </is>
       </c>
     </row>
@@ -1189,17 +1189,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La pierre de la terrasse est encore chaude. La lavande sent fort, tout près. Des tiges violettes bougent un peu. Des cigales chantent dans l'olivier. Un cerf-volant de papier attend sur la chaise. Il est bleu, avec une queue blanche. La ficelle est enroulée, un peu rêche. Je pose le chapeau sur le banc. Je remplis le verre d'eau. Tu entends les cigales, Mila ? Oui, maman. La pierre est chaude, hein ? Oui, papa. Je veux qu'il se lève. Au-dessus de la lavande. Un tout petit vent suffit. En ce moment, Mila prend le papier. Il est léger et un peu froissé.</t>
+          <t>La pierre de la terrasse tient la chaleur. Sous les paumes, elle brûle un peu. Elle est chaude, papa. Tu le sens, toi ? Oui, après la sieste. Tes yeux sont un peu lourds. Un peu, maman. Mila connaît cette terrasse. Des tiges violettes bougent près du mur. La lavande sent fort, près des pieds. Je pose le chapeau sur le banc. Je remplis le verre d'eau. Tu entends les cigales, Mila ? Oui, maman. Des cigales chantent dans l'olivier. Un cerf-volant de papier attend sur la chaise. Il est bleu, avec une queue blanche. La ficelle est rêche. Tu la tiens, Mila ? Oui, papa. Sur la pierre, un éclat de pierre brille. Il brille, maman ! Tu le vois, sur la pierre ? Oui, près de mes pieds. Je veux qu'il se lève, maintenant. Au-dessus des tiges. Un petit vent suffit. En ce moment, Mila prend le papier. Il est léger et un peu froissé. Monte ! Elle lève les bras trop vite. La ficelle claque. Le papier tombe contre les tiges. Oh. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Je le prends ! Le papier est dans les tiges. Tu le vois, Mila ? Les épaules de Mila tombent un peu. Ça serre, dans son ventre. Papa se baisse à sa hauteur.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La pierre de la terrasse est encore chaude. La lavande sent fort, tout près. Des tiges violettes bougent un peu. Des cigales chantent dans l'olivier. Un cerf-volant de papier attend sur la chaise. Il est bleu, avec une queue blanche. La ficelle est enroulée, un peu rêche. Je pose le chapeau sur le banc. Je remplis le verre d'eau. Tu entends les cigales, Mila ? Oui, maman. La pierre est chaude, hein ? Oui, papa. Je veux qu'il se lève. Au-dessus de la lavande. Un tout petit vent suffit. En ce moment, Mila prend le papier. Il est léger et un peu froissé.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La pierre de la terrasse tient la chaleur. Sous les paumes, elle brûle un peu. Elle est chaude, papa. Tu le sens, toi ? Oui, après la sieste. Tes yeux sont un peu lourds. Un peu, maman. Mila connaît cette terrasse. Des tiges violettes bougent près du mur. La lavande sent fort, près des pieds. Je pose le chapeau sur le banc. Je remplis le verre d'eau. Tu entends les cigales, Mila ? Oui, maman. Des cigales chantent dans l'olivier. Un cerf-volant de papier attend sur la chaise. Il est bleu, avec une queue blanche. La ficelle est rêche. Tu la tiens, Mila ? Oui, papa. Sur la pierre, un &lt;emphasis level="moderate"&gt;éclat de pierre&lt;/emphasis&gt; brille. Il brille, maman ! Tu le vois, sur la pierre ? Oui, près de mes pieds. Je veux qu'il se lève, maintenant. Au-dessus des tiges. Un petit vent suffit. En ce moment, Mila prend le papier. Il est léger et un peu froissé. Monte ! Elle lève les bras trop vite. La ficelle claque. Le papier tombe contre les tiges. Oh. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Je le prends ! Le papier est dans les tiges. Tu le vois, Mila ? Les épaules de Mila tombent un peu. Ça serre, dans son ventre. Papa se baisse à sa hauteur.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Le sable est chaud. Un oiseau chante. Lila a envie de jouer. [pause]</t>
+          <t>La pierre de la terrasse tient la chaleur. Sous les paumes, elle brûle un peu. Elle est chaude, papa. Tu le sens, toi ? Oui, après la sieste. Tes yeux sont un peu lourds. Un peu, maman. Mila connaît cette terrasse. Des tiges violettes bougent près du mur. La lavande sent fort, près des pieds. Je pose le chapeau sur le banc. Je remplis le verre d'eau. Tu entends les cigales, Mila ? Oui, maman. Des cigales chantent dans l'olivier. Un cerf-volant de papier attend sur la chaise. Il est bleu, avec une queue blanche. La ficelle est rêche. Tu la tiens, Mila ? Oui, papa. Sur la pierre, un &lt;emphasis&gt;éclat de pierre&lt;/emphasis&gt; brille. Il brille, maman ! Tu le vois, sur la pierre ? Oui, près de mes pieds. Je veux qu'il se lève, maintenant. Au-dessus des tiges. Un petit vent suffit. En ce moment, Mila prend le papier. Il est léger et un peu froissé. Monte ! Elle lève les bras trop vite. La ficelle claque. Le papier tombe contre les tiges. Oh. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Je le prends ! Le papier est dans les tiges. Tu le vois, Mila ? Les épaules de Mila tombent un peu. Ça serre, dans son ventre. Papa se baisse à sa hauteur. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1278,28 +1278,32 @@
       <c r="AG2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AH2" s="2" t="inlineStr"/>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>éclat de pierre</t>
+        </is>
+      </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1308,10 +1312,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1322,27 +1326,55 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience_curieuse puis découragement; intensite=2; destinataire=enfant; sous_texte=elle_veut_le_cerf_volant_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La pierre de la terrasse est encore chaude.
-narrateur|La lavande sent fort, tout près.
-narrateur|Des tiges violettes bougent un peu.
-narrateur|Des cigales chantent dans l'olivier.
-narrateur|Un cerf-volant de papier attend sur la chaise.
-narrateur|Il est bleu, avec une queue blanche.
-narrateur|La ficelle est enroulée, un peu rêche.
+          <t>narrateur|La pierre de la terrasse tient la chaleur.
+narrateur|Sous les paumes, elle brûle un peu.
+enfant-f|Elle est chaude, papa.
+papa|Tu le sens, toi ?
+enfant-f|Oui, après la sieste.
+maman|Tes yeux sont un peu lourds.
+enfant-f|Un peu, maman.
+narrateur|Mila connaît cette terrasse.
+narrateur|Des tiges violettes bougent près du mur.
+narrateur|La lavande sent fort, près des pieds.
 maman|Je pose le chapeau sur le banc.
 papa|Je remplis le verre d'eau.
 maman|Tu entends les cigales, Mila ?
 enfant-f|Oui, maman.
-papa|La pierre est chaude, hein ?
+narrateur|Des cigales chantent dans l'olivier.
+narrateur|Un cerf-volant de papier attend sur la chaise.
+narrateur|Il est bleu, avec une queue blanche.
+enfant-f|La ficelle est rêche.
+papa|Tu la tiens, Mila ?
 enfant-f|Oui, papa.
-enfant-f|Je veux qu'il se lève.
-enfant-f|Au-dessus de la lavande.
-maman|Un tout petit vent suffit.
+narrateur|Sur la pierre, un éclat de pierre brille.
+enfant-f|Il brille, maman !
+maman|Tu le vois, sur la pierre ?
+enfant-f|Oui, près de mes pieds.
+enfant-f|Je veux qu'il se lève, maintenant.
+enfant-f|Au-dessus des tiges.
+maman|Un petit vent suffit.
 narrateur|En ce moment, Mila prend le papier.
-narrateur|Il est léger et un peu froissé.</t>
+narrateur|Il est léger et un peu froissé.
+enfant-f|Monte !
+narrateur|Elle lève les bras trop vite.
+narrateur|La ficelle claque.
+narrateur|Le papier tombe contre les tiges.
+enfant-f|Oh.
+narrateur|Le sourire de Mila disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
+enfant-f|Je le prends !
+maman|Le papier est dans les tiges.
+papa|Tu le vois, Mila ?
+narrateur|Les épaules de Mila tombent un peu.
+narrateur|Ça serre, dans son ventre.
+narrateur|Papa se baisse à sa hauteur.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1374,17 +1406,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Aniss est sur la marche. Ses pieds restent à l'ombre. Mila tient la ficelle. Tu viens ? Je regarde. Mila accepte. On peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard. D'accord. Mila lève le papier. Le vent le fait trembler. Aniss reste sur la marche. Il regarde la queue blanche. Plus tard ? Plus tard. D'accord. Tu as accepté, Mila ? Oui, papa. Regarder, c'est une réponse. Une abeille passe sur la lavande. Elle fait un petit bruit. Tu l'entends, Mila ? Oui. On attend qu'elle parte. Mila tient le papier bas. L'abeille s'en va. Tu veux la ficelle ? Non. D'accord. Plusieurs réponses sont possibles. Le cerf-volant tremble encore. Aniss avance un pied. Puis il le retire.</t>
+          <t>Aniss est sur la marche. Ses pieds restent à l'ombre. Tu viens ? Aniss ne dit rien. Mila tient la ficelle trop près. Prends-la, maintenant ! Elle pousse la ficelle vers sa main. Aniss retire les doigts. Je regarde. Oh. Le papier tremble, trop bas. Le papier reste sous les tiges. Tu l'as vu, le papier ? Il ne se lève pas. Aniss est sur la marche. Plus tard ? Plus tard. Mila avance d'un pas. Aniss recule le pied. Tu veux la ficelle ? Non. La queue blanche traîne. Une abeille passe sur les tiges. Tu l'entends, Mila ? Oui. On attend qu'elle parte. Mila tient le papier bas. L'abeille s'en va. Les épaules restent basses.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Aniss est sur la marche. Ses pieds restent à l'ombre. Mila tient la ficelle. Tu viens ? Je regarde. Mila accepte. On peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard. D'accord. Mila lève le papier. Le vent le fait trembler. Aniss reste sur la marche. Il regarde la queue blanche. Plus tard ? Plus tard. D'accord. Tu as accepté, Mila ? Oui, papa. Regarder, c'est une réponse. Une abeille passe sur la lavande. Elle fait un petit bruit. Tu l'entends, Mila ? Oui. On attend qu'elle parte. Mila tient le papier bas. L'abeille s'en va. Tu veux la ficelle ? Non. D'accord. Plusieurs réponses sont possibles. Le cerf-volant tremble encore. Aniss avance un pied. Puis il le retire.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Aniss est sur la marche. Ses pieds restent à l'ombre. Tu viens ? Aniss ne dit rien. Mila tient la ficelle trop près. Prends-la, maintenant ! Elle pousse la ficelle vers sa main. Aniss retire les doigts. &lt;emphasis level="moderate"&gt;Je regarde&lt;/emphasis&gt;. Oh. Le papier tremble, trop bas. Le papier reste sous les tiges. Tu l'as vu, le papier ? Il ne se lève pas. Aniss est sur la marche. Plus tard ? Plus tard. Mila avance d'un pas. Aniss recule le pied. Tu veux la ficelle ? Non. La queue blanche traîne. Une abeille passe sur les tiges. Tu l'entends, Mila ? Oui. On attend qu'elle parte. Mila tient le papier bas. L'abeille s'en va. Les épaules restent basses.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Lila est au parc avec maman. Kenzo est près du bac. Lila va &lt;emphasis&gt;proposer&lt;/emphasis&gt; le seau. Elle dit : tu viens ? Kenzo dit : je regarde. Lila accepte. Maman dit : on peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard. Lila creuse. Kenzo reste au bord. Lila propose encore, tout doux : plus tard ? Kenzo dit : plus tard. Lila dit : d'accord. Elle accepte plusieurs réponses. [pause]</t>
+          <t>&lt;low-pitch&gt;Aniss est sur la marche. Ses pieds restent à l'ombre. Tu viens ? Aniss ne dit rien. Mila tient la ficelle trop près. Prends-la, maintenant ! Elle pousse la ficelle vers sa main. Aniss retire les doigts. &lt;emphasis&gt;Je regarde&lt;/emphasis&gt;. Oh. Le papier tremble, trop bas. Le papier reste sous les tiges. Tu l'as vu, le papier ? Il ne se lève pas. Aniss est sur la marche. Plus tard ? Plus tard. Mila avance d'un pas. Aniss recule le pied. Tu veux la ficelle ? Non. La queue blanche traîne. Une abeille passe sur les tiges. Tu l'entends, Mila ? Oui. On attend qu'elle parte. Mila tient le papier bas. L'abeille s'en va. Les épaules restent basses.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -1431,7 +1463,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1439,22 +1471,26 @@
         </is>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr"/>
+          <t>-2st</t>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="inlineStr">
+        <is>
+          <t>low-pitch</t>
+        </is>
+      </c>
       <c r="AF3" s="2" t="inlineStr">
         <is>
           <t>medium</t>
@@ -1465,30 +1501,30 @@
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
-          <t>proposer</t>
+          <t>Je regarde</t>
         </is>
       </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>450</v>
+        <v>520</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>tense</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1497,60 +1533,56 @@
         </is>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AS3" s="2" t="n">
         <v>100</v>
       </c>
       <c r="AT3" s="2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AU3" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AV3" s="2" t="inlineStr">
+        <is>
+          <t>arc=obstacle; intention=alerter_sans_effrayer; emotion=élan puis retenue; intensite=2; destinataire=enfant; sous_texte=aniss_regarde_ne_prend_pas_la_ficelle; tempo=resserré; sourire=aucun; respiration=retenue</t>
+        </is>
+      </c>
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|Aniss est sur la marche.
 narrateur|Ses pieds restent à l'ombre.
-narrateur|Mila tient la ficelle.
 enfant-f|Tu viens ?
+narrateur|Aniss ne dit rien.
+narrateur|Mila tient la ficelle trop près.
+enfant-f|Prends-la, maintenant !
+narrateur|Elle pousse la ficelle vers sa main.
+narrateur|Aniss retire les doigts.
 copain|Je regarde.
-narrateur|Mila accepte.
-maman|On peut proposer.
-maman|On peut accepter plusieurs réponses.
-papa|Oui.
-papa|Non.
-papa|Regarder.
-papa|Plus tard.
-enfant-f|D'accord.
-narrateur|Mila lève le papier.
-narrateur|Le vent le fait trembler.
-narrateur|Aniss reste sur la marche.
-narrateur|Il regarde la queue blanche.
+enfant-f|Oh.
+narrateur|Le papier tremble, trop bas.
+narrateur|Le papier reste sous les tiges.
+papa|Tu l'as vu, le papier ?
+enfant-f|Il ne se lève pas.
+maman|Aniss est sur la marche.
 enfant-f|Plus tard ?
 copain|Plus tard.
-enfant-f|D'accord.
-papa|Tu as accepté, Mila ?
-enfant-f|Oui, papa.
-maman|Regarder, c'est une réponse.
-narrateur|Une abeille passe sur la lavande.
-narrateur|Elle fait un petit bruit.
+narrateur|Mila avance d'un pas.
+narrateur|Aniss recule le pied.
+enfant-f|Tu veux la ficelle ?
+copain|Non.
+narrateur|La queue blanche traîne.
+narrateur|Une abeille passe sur les tiges.
 maman|Tu l'entends, Mila ?
 enfant-f|Oui.
 papa|On attend qu'elle parte.
 narrateur|Mila tient le papier bas.
 narrateur|L'abeille s'en va.
-enfant-f|Tu veux la ficelle ?
-copain|Non.
-enfant-f|D'accord.
-papa|Plusieurs réponses sont possibles.
-narrateur|Le cerf-volant tremble encore.
-narrateur|Aniss avance un pied.
-narrateur|Puis il le retire.</t>
+narrateur|Les épaules restent basses.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1587,12 +1619,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Mila invite Aniss. Que fait-elle ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Mila &lt;emphasis level="moderate"&gt;invite&lt;/emphasis&gt; Aniss. Que fait-elle ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Lila invite Kenzo. Que fait-elle si Kenzo dit non ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Mila &lt;emphasis&gt;invite&lt;/emphasis&gt; Aniss. Que fait-elle ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1655,7 +1687,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1666,7 +1698,7 @@
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1681,34 +1713,38 @@
       <c r="AE4" s="2" t="inlineStr"/>
       <c r="AF4" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>invite</t>
+        </is>
+      </c>
       <c r="AI4" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1723,17 +1759,17 @@
         <v>0.86</v>
       </c>
       <c r="AS4" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT4" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU4" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=elle_invite_et_prend_la_reponse_d_aniss; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -1766,17 +1802,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Mila a su proposer. Elle a su accepter plusieurs réponses. Aniss a dit regarder, puis plus tard. Oui. Tout ça va. J'ai dit d'accord. Bravo. Tu as tenu la ficelle. Le papier se lève un peu. L'ombre passe sur la lavande. Tu vois l'ombre, Aniss ? Je regarde. C'est une réponse. Mila recule d'un pas. La queue blanche danse. Une tige de lavande se plie. Le vent est juste assez.</t>
+          <t>Mila avance trop vite vers Aniss. Tu viens, maintenant ! Sa voix se mélange au vent. Oh. Aniss reste sur la marche. Mila refuse de foncer. Elle referme la main. Elle regarde la pierre, un instant. Tu veux venir près de la pierre ? Papa s'accroupit à la même hauteur. Mila pose un pied sur la pierre chaude. Tu viens ? Elle attend. Aniss ne dit rien. D'accord. Je regarde. Merci, Mila. Papa a entendu toute la phrase. Le ventre de Mila se desserre. Les épaules se relèvent un peu. Tu as les mains au chaud ? Un peu, maman. Sur la pierre, un éclat de pierre tient. Il est là. Mila lève le papier, sans tirer. Un petit vent prend la queue. Je vois. Il tremble un peu. Il se lève.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Mila a su proposer. Elle a su accepter plusieurs réponses. Aniss a dit regarder, puis plus tard. Oui. Tout ça va. J'ai dit d'accord. Bravo. Tu as tenu la ficelle. Le papier se lève un peu. L'ombre passe sur la lavande. Tu vois l'ombre, Aniss ? Je regarde. C'est une réponse. Mila recule d'un pas. La queue blanche danse. Une tige de lavande se plie. Le vent est juste assez.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila avance trop vite vers Aniss. Tu viens, maintenant ! Sa voix se mélange au vent. Oh. Aniss reste sur la marche. Mila refuse de foncer. Elle referme la main. Elle regarde la pierre, un instant. Tu veux venir près de la pierre ? Papa s'accroupit à la même hauteur. Mila pose un pied sur la pierre chaude. Tu viens ? Elle attend. Aniss ne dit rien. &lt;emphasis level="moderate"&gt;D'accord&lt;/emphasis&gt;. Je regarde. Merci, Mila. Papa a entendu toute la phrase. Le ventre de Mila se desserre. Les épaules se relèvent un peu. Tu as les mains au chaud ? Un peu, maman. Sur la pierre, un éclat de pierre tient. Il est là. Mila lève le papier, sans tirer. Un petit vent prend la queue. Je vois. Il tremble un peu. Il se lève.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Lila a su &lt;emphasis&gt;proposer&lt;/emphasis&gt;. Elle a su accepter plusieurs réponses. [pause]</t>
+          <t>Mila avance trop vite vers Aniss. Tu viens, maintenant ! Sa voix se mélange au vent. Oh. Aniss reste sur la marche. Mila refuse de foncer. Elle referme la main. Elle regarde la pierre, un instant. Tu veux venir près de la pierre ? Papa s'accroupit à la même hauteur. Mila pose un pied sur la pierre chaude. Tu viens ? Elle attend. Aniss ne dit rien. &lt;emphasis&gt;D'accord&lt;/emphasis&gt;. Je regarde. Merci, Mila. Papa a entendu toute la phrase. Le ventre de Mila se desserre. Les épaules se relèvent un peu. Tu as les mains au chaud ? Un peu, maman. Sur la pierre, un éclat de pierre tient. Il est là. Mila lève le papier, sans tirer. Un petit vent prend la queue. Je vois. Il tremble un peu. Il se lève. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1823,7 +1859,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1831,10 +1867,10 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1857,30 +1893,30 @@
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>proposer</t>
+          <t>D'accord</t>
         </is>
       </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1889,10 +1925,10 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
@@ -1905,28 +1941,40 @@
       </c>
       <c r="AV5" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_le_geste; emotion=retenue puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=d_accord_laisse_aniss_regarder; tempo=naturel; sourire=léger; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Mila a su proposer.
-narrateur|Elle a su accepter plusieurs réponses.
-papa|Aniss a dit regarder, puis plus tard.
-maman|Oui.
-maman|Tout ça va.
-enfant-f|J'ai dit d'accord.
-papa|Bravo.
-papa|Tu as tenu la ficelle.
-narrateur|Le papier se lève un peu.
-narrateur|L'ombre passe sur la lavande.
-enfant-f|Tu vois l'ombre, Aniss ?
+          <t>narrateur|Mila avance trop vite vers Aniss.
+enfant-f|Tu viens, maintenant !
+narrateur|Sa voix se mélange au vent.
+enfant-f|Oh.
+narrateur|Aniss reste sur la marche.
+narrateur|Mila refuse de foncer.
+narrateur|Elle referme la main.
+narrateur|Elle regarde la pierre, un instant.
+papa|Tu veux venir près de la pierre ?
+narrateur|Papa s'accroupit à la même hauteur.
+narrateur|Mila pose un pied sur la pierre chaude.
+enfant-f|Tu viens ?
+narrateur|Elle attend.
+narrateur|Aniss ne dit rien.
+enfant-f|D'accord.
 copain|Je regarde.
-maman|C'est une réponse.
-narrateur|Mila recule d'un pas.
-narrateur|La queue blanche danse.
-narrateur|Une tige de lavande se plie.
-papa|Le vent est juste assez.</t>
+papa|Merci, Mila.
+narrateur|Papa a entendu toute la phrase.
+narrateur|Le ventre de Mila se desserre.
+narrateur|Les épaules se relèvent un peu.
+maman|Tu as les mains au chaud ?
+enfant-f|Un peu, maman.
+narrateur|Sur la pierre, un éclat de pierre tient.
+enfant-f|Il est là.
+narrateur|Mila lève le papier, sans tirer.
+narrateur|Un petit vent prend la queue.
+copain|Je vois.
+maman|Il tremble un peu.
+enfant-f|Il se lève.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1958,17 +2006,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On repose le papier ? Encore un peu. L'ombre glisse sur deux tiges. Aniss suit des yeux. Tu as fini de jouer, Mila ? Oui, papa. Mila pose le cerf-volant. Il retrouve la chaise. Aniss secoue un pied. Un peu de poussière tombe. Merci, Aniss. Tu as regardé. La lavande sent encore. L'ombre était jolie. Oui.</t>
+          <t>Mila tire la ficelle trop vite. Au-dessus des tiges, d'un coup ! Le papier plonge dans les tiges. Oh. Mila avance les mains. Puis elle s'arrête net. Attends, je regarde. Papa attend, sans parler. Mila observe la pierre, écoute les cigales. Sur la pierre, un éclat de pierre luit. Là, près de mes pieds. Mila recule d'un pas. Elle tient la ficelle des deux mains. Il est léger, papa. Tu le portes vers le vent ? Oui, papa. On avance ? Oui, maman. Un petit vent arrive. Le papier se lève un peu. L'ombre passe sur les tiges. Tu vois l'ombre, Aniss ? Je regarde. Aniss avance un pied. Puis il le retire. D'accord. On reste là. La queue blanche danse. Une tige violette se plie. Le vent est juste assez.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>On repose le papier ? Encore un peu. L'ombre glisse sur deux tiges. Aniss suit des yeux. Tu as fini de jouer, Mila ? Oui, papa. Mila pose le cerf-volant. Il retrouve la chaise. Aniss secoue un pied. Un peu de poussière tombe. Merci, Aniss. Tu as regardé. La lavande sent encore. L'ombre était jolie. Oui.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila tire la ficelle trop vite. Au-dessus des tiges, d'un coup ! Le papier plonge dans les tiges. Oh. Mila avance les mains. Puis elle s'arrête net. Attends, je regarde. Papa attend, sans parler. Mila observe la pierre, écoute les cigales. Sur la pierre, un &lt;emphasis level="moderate"&gt;éclat de pierre&lt;/emphasis&gt; luit. Là, près de mes pieds. Mila recule d'un pas. Elle tient la ficelle des deux mains. Il est léger, papa. Tu le portes vers le vent ? Oui, papa. On avance ? Oui, maman. Un petit vent arrive. Le papier se lève un peu. L'ombre passe sur les tiges. Tu vois l'ombre, Aniss ? Je regarde. Aniss avance un pied. Puis il le retire. D'accord. On reste là. La queue blanche danse. Une tige violette se plie. Le vent est juste assez.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Maman range le seau. Lila donne la &lt;emphasis&gt;main&lt;/emphasis&gt;. [pause]</t>
+          <t>Mila tire la ficelle trop vite. Au-dessus des tiges, d'un coup ! Le papier plonge dans les tiges. Oh. Mila avance les mains. Puis elle s'arrête net. Attends, je regarde. Papa attend, sans parler. Mila observe la pierre, écoute les cigales. Sur la pierre, un &lt;emphasis&gt;éclat de pierre&lt;/emphasis&gt; luit. Là, près de mes pieds. Mila recule d'un pas. Elle tient la ficelle des deux mains. Il est léger, papa. Tu le portes vers le vent ? Oui, papa. On avance ? Oui, maman. Un petit vent arrive. Le papier se lève un peu. L'ombre passe sur les tiges. Tu vois l'ombre, Aniss ? Je regarde. Aniss avance un pied. Puis il le retire. D'accord. On reste là. La queue blanche danse. Une tige violette se plie. Le vent est juste assez. [pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2015,7 +2063,7 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
@@ -2023,10 +2071,10 @@
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2049,30 +2097,30 @@
       </c>
       <c r="AH6" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>éclat de pierre</t>
         </is>
       </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>lively</t>
         </is>
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.37</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2081,10 +2129,10 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AS6" s="2" t="n">
         <v>100</v>
@@ -2095,24 +2143,48 @@
       <c r="AU6" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=action; intention=entraîner; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=elle_refuse_de_foncer_retrouve_l_eclat_de_pierre; tempo=vif puis posé; sourire=léger; respiration=courte</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>maman|On repose le papier ?
-enfant-f|Encore un peu.
-narrateur|L'ombre glisse sur deux tiges.
-narrateur|Aniss suit des yeux.
-papa|Tu as fini de jouer, Mila ?
+          <t>narrateur|Mila tire la ficelle trop vite.
+enfant-f|Au-dessus des tiges, d'un coup !
+narrateur|Le papier plonge dans les tiges.
+enfant-f|Oh.
+narrateur|Mila avance les mains.
+narrateur|Puis elle s'arrête net.
+enfant-f|Attends, je regarde.
+narrateur|Papa attend, sans parler.
+narrateur|Mila observe la pierre, écoute les cigales.
+narrateur|Sur la pierre, un éclat de pierre luit.
+enfant-f|Là, près de mes pieds.
+narrateur|Mila recule d'un pas.
+narrateur|Elle tient la ficelle des deux mains.
+enfant-f|Il est léger, papa.
+papa|Tu le portes vers le vent ?
 enfant-f|Oui, papa.
-narrateur|Mila pose le cerf-volant.
-narrateur|Il retrouve la chaise.
-narrateur|Aniss secoue un pied.
-narrateur|Un peu de poussière tombe.
-maman|Merci, Aniss.
-maman|Tu as regardé.
-papa|La lavande sent encore.
-enfant-f|L'ombre était jolie.
-papa|Oui.</t>
+maman|On avance ?
+enfant-f|Oui, maman.
+narrateur|Un petit vent arrive.
+narrateur|Le papier se lève un peu.
+narrateur|L'ombre passe sur les tiges.
+enfant-f|Tu vois l'ombre, Aniss ?
+copain|Je regarde.
+narrateur|Aniss avance un pied.
+narrateur|Puis il le retire.
+enfant-f|D'accord.
+maman|On reste là.
+narrateur|La queue blanche danse.
+narrateur|Une tige violette se plie.
+papa|Le vent est juste assez.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>vent,papier</t>
         </is>
       </c>
     </row>
@@ -2139,17 +2211,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Le cerf-volant bleu dort sur la chaise. J'ai proposé. J'ai accepté. Plusieurs réponses sont possibles. Oui. Les cigales chantent encore.</t>
+          <t>Le papier brillait, papa. Tu le vois, comme sur la chaise ? Oui, un peu froissé. Mila pose le cerf-volant. Il retrouve la chaise. On le garde près de nous ? Oui, maman. La lavande sentait fort. Les tiges sont derrière nous. Aniss secoue un pied. Un peu de poussière tombe. On rentre ? Oui. Les joues de Mila se réchauffent. La pierre reste chaude sous la main. Elle est chaude. Comme tout à l'heure ? Oui, maman. La lumière est pâle, toi ? Oui, papa. Un éclat de pierre reste pâle.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Le cerf-volant bleu dort sur la chaise. J'ai proposé. J'ai accepté. Plusieurs réponses sont possibles. Oui. Les cigales chantent encore.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le papier brillait, papa. Tu le vois, comme sur la chaise ? Oui, un peu froissé. Mila pose le cerf-volant. Il retrouve la chaise. On le garde près de nous ? Oui, maman. La lavande sentait fort. Les tiges sont derrière nous. Aniss secoue un pied. Un peu de poussière tombe. On rentre ? Oui. Les joues de Mila se réchauffent. La pierre reste chaude sous la main. Elle est chaude. Comme tout à l'heure ? Oui, maman. La lumière est pâle, toi ? Oui, papa. Un &lt;emphasis level="moderate"&gt;éclat de pierre&lt;/emphasis&gt; reste pâle.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le papier brillait, papa. Tu le vois, comme sur la chaise ? Oui, un peu froissé. Mila pose le cerf-volant. Il retrouve la chaise. On le garde près de nous ? Oui, maman. La lavande sentait fort. Les tiges sont derrière nous. Aniss secoue un pied. Un peu de poussière tombe. On rentre ? Oui. Les joues de Mila se réchauffent. La pierre reste chaude sous la main. Elle est chaude. Comme tout à l'heure ? Oui, maman. La lumière est pâle, toi ? Oui, papa. Un &lt;emphasis&gt;éclat de pierre&lt;/emphasis&gt; reste pâle.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -2196,18 +2268,18 @@
         </is>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
@@ -2216,12 +2288,12 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE7" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF7" s="2" t="inlineStr">
@@ -2230,17 +2302,21 @@
         </is>
       </c>
       <c r="AG7" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH7" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH7" s="2" t="inlineStr">
+        <is>
+          <t>éclat de pierre</t>
+        </is>
+      </c>
       <c r="AI7" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ7" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK7" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL7" s="2" t="inlineStr">
         <is>
@@ -2249,11 +2325,11 @@
       </c>
       <c r="AM7" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN7" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO7" s="2" t="inlineStr"/>
       <c r="AP7" s="2" t="inlineStr">
@@ -2262,29 +2338,53 @@
         </is>
       </c>
       <c r="AQ7" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AR7" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AS7" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT7" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU7" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV7" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV7" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse_et_fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_de_pierre_reste_pale; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|Le cerf-volant bleu dort sur la chaise.
-enfant-f|J'ai proposé.
-enfant-f|J'ai accepté.
-maman|Plusieurs réponses sont possibles.
-papa|Oui.
-narrateur|Les cigales chantent encore.</t>
+          <t>enfant-f|Le papier brillait, papa.
+papa|Tu le vois, comme sur la chaise ?
+enfant-f|Oui, un peu froissé.
+narrateur|Mila pose le cerf-volant.
+narrateur|Il retrouve la chaise.
+maman|On le garde près de nous ?
+enfant-f|Oui, maman.
+enfant-f|La lavande sentait fort.
+maman|Les tiges sont derrière nous.
+narrateur|Aniss secoue un pied.
+narrateur|Un peu de poussière tombe.
+papa|On rentre ?
+enfant-f|Oui.
+narrateur|Les joues de Mila se réchauffent.
+narrateur|La pierre reste chaude sous la main.
+enfant-f|Elle est chaude.
+maman|Comme tout à l'heure ?
+enfant-f|Oui, maman.
+papa|La lumière est pâle, toi ?
+enfant-f|Oui, papa.
+narrateur|Un éclat de pierre reste pâle.</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>terrasse</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2383,6 +2483,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
